--- a/employees.xlsx
+++ b/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uncommonStudent\Desktop\python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063AF232-566E-4BEE-A811-6D55BD1573DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BB9332-2532-4B9C-B700-FD534C8E446F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3B682B7B-97E0-48BE-84DD-2D27749716D8}"/>
   </bookViews>
